--- a/Course 4/Kursach/Графики.xlsx
+++ b/Course 4/Kursach/Графики.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\University\Kursach\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F9B061C-18D9-413C-A393-47352D1B4318}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D3AD70D-8C47-4F0E-ABF0-885F2B2951B8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1800" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="33">
   <si>
     <t>Объем файла (слов)</t>
   </si>
@@ -130,8 +130,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="170" formatCode="0.0000"/>
+  <numFmts count="3">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _₽_-;\-* #,##0.00\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -166,19 +168,29 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Процентный" xfId="1" builtinId="5"/>
+    <cellStyle name="Финансовый" xfId="2" builtinId="3"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -191,6 +203,3060 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$B$16</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ChaCha20 Шифрование</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$B$17:$B$22</c:f>
+              <c:numCache>
+                <c:formatCode>0.000000</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1.0154E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0015899999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.0108799999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.0138100000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.0175699999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.0203E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-523C-4FBB-B14A-C2E5B9F6DB0A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$C$16</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ChaCha20 Дешифрование</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$C$17:$C$22</c:f>
+              <c:numCache>
+                <c:formatCode>0.000000</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2.97E-5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.7700000000000002E-5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.6100000000000003E-5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.49E-5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.3999999999999997E-5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.048E-4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-523C-4FBB-B14A-C2E5B9F6DB0A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$D$16</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Twofish Шифрование</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$D$17:$D$22</c:f>
+              <c:numCache>
+                <c:formatCode>0.000000</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>8.164E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.5457000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.4479999999999997E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.5202999999999997E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.7766999999999993E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.4257299999999999E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-523C-4FBB-B14A-C2E5B9F6DB0A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$E$16</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Twofish Дешифрование</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$E$17:$E$22</c:f>
+              <c:numCache>
+                <c:formatCode>0.000000</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>7.804E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.6770000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.4745000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.7444000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.6641999999999995E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.4235900000000001E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-523C-4FBB-B14A-C2E5B9F6DB0A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1823310432"/>
+        <c:axId val="1928804832"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1823310432"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ru-RU"/>
+                  <a:t>Объем</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="ru-RU" baseline="0"/>
+                  <a:t> файла</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ru-RU"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1928804832"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:tickLblSkip val="1"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1928804832"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ru-RU"/>
+                  <a:t>Время шифрования</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ru-RU"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.000000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1823310432"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$B$16</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ChaCha20 Шифрование</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$B$17:$B$22</c:f>
+              <c:numCache>
+                <c:formatCode>0.000000</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1.0154E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0015899999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.0108799999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.0138100000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.0175699999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.0203E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9C71-438E-9F9D-D98954C75041}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$C$16</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ChaCha20 Дешифрование</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$C$17:$C$22</c:f>
+              <c:numCache>
+                <c:formatCode>0.000000</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2.97E-5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.7700000000000002E-5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.6100000000000003E-5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.49E-5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.3999999999999997E-5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.048E-4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9C71-438E-9F9D-D98954C75041}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="378655904"/>
+        <c:axId val="216145888"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="378655904"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="216145888"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="216145888"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.000000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="378655904"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$D$16</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Twofish Шифрование</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$D$17:$D$22</c:f>
+              <c:numCache>
+                <c:formatCode>0.000000</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>8.164E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.5457000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.4479999999999997E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.5202999999999997E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.7766999999999993E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.4257299999999999E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7A45-4AA9-838A-BC2BBD5E5CEF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$E$16</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Twofish Дешифрование</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$E$17:$E$22</c:f>
+              <c:numCache>
+                <c:formatCode>0.000000</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>7.804E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.6770000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.4745000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.7444000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.6641999999999995E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.4235900000000001E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-7A45-4AA9-838A-BC2BBD5E5CEF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="77298160"/>
+        <c:axId val="79395712"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="77298160"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="79395712"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="79395712"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.000000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="77298160"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>31376</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>81475</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>586069</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>119575</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Диаграмма 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBF258B8-0B31-464C-B658-7A60769C3B70}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>190499</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>142874</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Диаграмма 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7A31118-87F8-4446-B8F1-30B8C52F5600}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Диаграмма 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5066D473-ED4C-4F32-97EF-958CF0A89701}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -456,7 +3522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -624,109 +3690,131 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
         <v>1000</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="2">
+        <v>1.0154E-2</v>
+      </c>
+      <c r="C17" s="3">
+        <v>2.97E-5</v>
+      </c>
+      <c r="D17" s="3">
+        <v>8.164E-4</v>
+      </c>
+      <c r="E17" s="3">
+        <v>7.804E-4</v>
+      </c>
+      <c r="F17" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
+        <v>3000</v>
+      </c>
+      <c r="B18" s="2">
+        <v>1.0015899999999999E-2</v>
+      </c>
+      <c r="C18" s="3">
+        <v>3.7700000000000002E-5</v>
+      </c>
+      <c r="D18" s="3">
+        <v>2.5457000000000001E-3</v>
+      </c>
+      <c r="E18" s="3">
+        <v>2.6770000000000001E-3</v>
+      </c>
+      <c r="F18" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
+        <v>5000</v>
+      </c>
+      <c r="B19" s="2">
+        <v>1.0108799999999999E-2</v>
+      </c>
+      <c r="C19" s="3">
+        <v>3.6100000000000003E-5</v>
+      </c>
+      <c r="D19" s="3">
+        <v>4.4479999999999997E-3</v>
+      </c>
+      <c r="E19" s="3">
+        <v>4.4745000000000002E-3</v>
+      </c>
+      <c r="F19" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
+        <v>8000</v>
+      </c>
+      <c r="B20" s="2">
+        <v>1.0138100000000001E-2</v>
+      </c>
+      <c r="C20" s="3">
+        <v>5.49E-5</v>
+      </c>
+      <c r="D20" s="3">
+        <v>7.5202999999999997E-3</v>
+      </c>
+      <c r="E20" s="3">
+        <v>7.7444000000000002E-3</v>
+      </c>
+      <c r="F20" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="4">
+        <v>10000</v>
+      </c>
+      <c r="B21" s="2">
+        <v>1.0175699999999999E-2</v>
+      </c>
+      <c r="C21" s="3">
+        <v>6.3999999999999997E-5</v>
+      </c>
+      <c r="D21" s="3">
+        <v>9.7766999999999993E-3</v>
+      </c>
+      <c r="E21" s="3">
+        <v>9.6641999999999995E-3</v>
+      </c>
+      <c r="F21" s="5">
         <v>5</v>
       </c>
-      <c r="C17" t="s">
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
+        <v>20000</v>
+      </c>
+      <c r="B22" s="2">
+        <v>1.0203E-2</v>
+      </c>
+      <c r="C22" s="3">
+        <v>1.048E-4</v>
+      </c>
+      <c r="D22" s="3">
+        <v>2.4257299999999999E-2</v>
+      </c>
+      <c r="E22" s="3">
+        <v>2.4235900000000001E-2</v>
+      </c>
+      <c r="F22" s="5">
         <v>6</v>
       </c>
-      <c r="D17" t="s">
-        <v>7</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>3000</v>
-      </c>
-      <c r="B18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>5000</v>
-      </c>
-      <c r="B19" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" t="s">
-        <v>14</v>
-      </c>
-      <c r="D19" t="s">
-        <v>15</v>
-      </c>
-      <c r="E19" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>8000</v>
-      </c>
-      <c r="B20" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" t="s">
-        <v>18</v>
-      </c>
-      <c r="D20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E20" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>10000</v>
-      </c>
-      <c r="B21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" t="s">
-        <v>23</v>
-      </c>
-      <c r="E21" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>20000</v>
-      </c>
-      <c r="B22" t="s">
-        <v>25</v>
-      </c>
-      <c r="C22" t="s">
-        <v>26</v>
-      </c>
-      <c r="D22" t="s">
-        <v>27</v>
-      </c>
-      <c r="E22" t="s">
-        <v>28</v>
-      </c>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F23" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>